--- a/05. Res/modelos/coeficientes_lognormal.xlsx
+++ b/05. Res/modelos/coeficientes_lognormal.xlsx
@@ -466,13 +466,13 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>4.68510460031892</v>
+        <v>4.71127929873248</v>
       </c>
       <c r="C2" t="n">
-        <v>0.103410194362788</v>
+        <v>0.10589785363125</v>
       </c>
       <c r="D2" t="n">
-        <v>45.3060225753219</v>
+        <v>44.4889026281662</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -483,16 +483,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>0.123186889565111</v>
+        <v>0.114615433542758</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0672576994591427</v>
+        <v>0.0667433254989389</v>
       </c>
       <c r="D3" t="n">
-        <v>1.83156561339038</v>
+        <v>1.71725685955789</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0670352527549193</v>
+        <v>0.085952051501347</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>0.130282903512371</v>
+        <v>0.131528251663675</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0622923414644199</v>
+        <v>0.0618217797896261</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0914754598972</v>
+        <v>2.12753906651109</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0365016218593818</v>
+        <v>0.0333909206093379</v>
       </c>
     </row>
     <row r="5">
@@ -517,16 +517,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0649419333168612</v>
+        <v>0.0561310186016323</v>
       </c>
       <c r="C5" t="n">
-        <v>1.26247978930775</v>
+        <v>1.26521191149604</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0514399785777722</v>
+        <v>0.0443649147558694</v>
       </c>
       <c r="E5" t="n">
-        <v>0.958975588290136</v>
+        <v>0.964614094553442</v>
       </c>
     </row>
     <row r="6">
@@ -534,16 +534,16 @@
         <v>9</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.0180624768532492</v>
+        <v>-0.0506965192881001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0224565016209996</v>
+        <v>0.022412838156875</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.804331732435053</v>
+        <v>-2.26194107739762</v>
       </c>
       <c r="E6" t="n">
-        <v>0.421217692587599</v>
+        <v>0.0237147128205497</v>
       </c>
     </row>
     <row r="7">
@@ -551,16 +551,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0812043961352665</v>
+        <v>0.0966727259156974</v>
       </c>
       <c r="C7" t="n">
-        <v>0.081914815733738</v>
+        <v>0.0829118608234632</v>
       </c>
       <c r="D7" t="n">
-        <v>0.991327336915697</v>
+        <v>1.16596980161299</v>
       </c>
       <c r="E7" t="n">
-        <v>0.321541168903704</v>
+        <v>0.243644438669862</v>
       </c>
     </row>
     <row r="8">
@@ -568,16 +568,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0626474987891499</v>
+        <v>0.0501462236868316</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0838006064655862</v>
+        <v>0.0850013149698212</v>
       </c>
       <c r="D8" t="n">
-        <v>0.747578107503039</v>
+        <v>0.589946446177161</v>
       </c>
       <c r="E8" t="n">
-        <v>0.454725960274375</v>
+        <v>0.555235078316416</v>
       </c>
     </row>
     <row r="9">
@@ -585,16 +585,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0515581771631753</v>
+        <v>0.0256456746533621</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0867948040321754</v>
+        <v>0.0878939690740891</v>
       </c>
       <c r="D9" t="n">
-        <v>0.594023775248831</v>
+        <v>0.291779685495195</v>
       </c>
       <c r="E9" t="n">
-        <v>0.552504838670159</v>
+        <v>0.770458948908579</v>
       </c>
     </row>
     <row r="10">
@@ -602,16 +602,16 @@
         <v>13</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0445709828333358</v>
+        <v>0.035553679602321</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0891004942308771</v>
+        <v>0.0902536383753414</v>
       </c>
       <c r="D10" t="n">
-        <v>0.500232722815696</v>
+        <v>0.393930707308025</v>
       </c>
       <c r="E10" t="n">
-        <v>0.616918287340812</v>
+        <v>0.693637570005821</v>
       </c>
     </row>
     <row r="11">
@@ -619,16 +619,16 @@
         <v>14</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0496678250484276</v>
+        <v>0.0383125028060342</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0941485412505448</v>
+        <v>0.0949151505568989</v>
       </c>
       <c r="D11" t="n">
-        <v>0.527547473266243</v>
+        <v>0.403650024060879</v>
       </c>
       <c r="E11" t="n">
-        <v>0.597820973092031</v>
+        <v>0.686475614106955</v>
       </c>
     </row>
     <row r="12">
@@ -636,16 +636,16 @@
         <v>15</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.0301351421467408</v>
+        <v>-0.0153969485824704</v>
       </c>
       <c r="C12" t="n">
-        <v>0.101631009038842</v>
+        <v>0.104255589504446</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.296515231244272</v>
+        <v>-0.147684634038866</v>
       </c>
       <c r="E12" t="n">
-        <v>0.766840590510891</v>
+        <v>0.882593563022875</v>
       </c>
     </row>
     <row r="13">
@@ -653,16 +653,16 @@
         <v>16</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0387681136275485</v>
+        <v>0.0156106270754481</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0969463258094086</v>
+        <v>0.0995476005277739</v>
       </c>
       <c r="D13" t="n">
-        <v>0.399892551923676</v>
+        <v>0.156815704172526</v>
       </c>
       <c r="E13" t="n">
-        <v>0.689241142250858</v>
+        <v>0.875392120367257</v>
       </c>
     </row>
     <row r="14">
@@ -670,16 +670,16 @@
         <v>17</v>
       </c>
       <c r="B14" t="n">
-        <v>0.00541947846638105</v>
+        <v>0.00732202106868063</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0966457021764546</v>
+        <v>0.099321033297511</v>
       </c>
       <c r="D14" t="n">
-        <v>0.056075731712169</v>
+        <v>0.0737207500323512</v>
       </c>
       <c r="E14" t="n">
-        <v>0.955282196089504</v>
+        <v>0.941233530521259</v>
       </c>
     </row>
     <row r="15">
@@ -687,16 +687,16 @@
         <v>18</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.0115288543267361</v>
+        <v>0.0182328028395311</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0992605362640279</v>
+        <v>0.101930830432337</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.116147411253854</v>
+        <v>0.178874269562969</v>
       </c>
       <c r="E15" t="n">
-        <v>0.907537211739959</v>
+        <v>0.858038744234043</v>
       </c>
     </row>
     <row r="16">
@@ -704,16 +704,16 @@
         <v>19</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0218067215968786</v>
+        <v>0.016693674339917</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0308705159561236</v>
+        <v>0.0305427899374419</v>
       </c>
       <c r="D16" t="n">
-        <v>0.70639316906373</v>
+        <v>0.546566779724746</v>
       </c>
       <c r="E16" t="n">
-        <v>0.479954234369946</v>
+        <v>0.584684195787482</v>
       </c>
     </row>
     <row r="17">
@@ -721,16 +721,16 @@
         <v>20</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0003394093381872</v>
+        <v>0.0122316583697571</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0336183871005747</v>
+        <v>0.033260705285147</v>
       </c>
       <c r="D17" t="n">
-        <v>0.010095943543389</v>
+        <v>0.367751022261676</v>
       </c>
       <c r="E17" t="n">
-        <v>0.991944868668766</v>
+        <v>0.713063869469753</v>
       </c>
     </row>
     <row r="18">
@@ -738,16 +738,16 @@
         <v>21</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0116835021550842</v>
+        <v>-0.0251163947690158</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0634805936764328</v>
+        <v>0.0634714010270273</v>
       </c>
       <c r="D18" t="n">
-        <v>0.184048407213017</v>
+        <v>-0.395711995680083</v>
       </c>
       <c r="E18" t="n">
-        <v>0.853977876067933</v>
+        <v>0.692322903653048</v>
       </c>
     </row>
     <row r="19">
@@ -755,16 +755,16 @@
         <v>22</v>
       </c>
       <c r="B19" t="n">
-        <v>0.116022858822239</v>
+        <v>0.0945817276524132</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0346173998444825</v>
+        <v>0.0342380422574226</v>
       </c>
       <c r="D19" t="n">
-        <v>3.35157635592124</v>
+        <v>2.76247476246714</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000805440038323612</v>
+        <v>0.00574320018182119</v>
       </c>
     </row>
     <row r="20">
@@ -772,16 +772,16 @@
         <v>23</v>
       </c>
       <c r="B20" t="n">
-        <v>0.106986701122481</v>
+        <v>0.0977234772943658</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0377727875668316</v>
+        <v>0.0373753690198565</v>
       </c>
       <c r="D20" t="n">
-        <v>2.83237505130352</v>
+        <v>2.6146491621915</v>
       </c>
       <c r="E20" t="n">
-        <v>0.00462629160675247</v>
+        <v>0.0089404822459533</v>
       </c>
     </row>
     <row r="21">
@@ -789,16 +789,16 @@
         <v>24</v>
       </c>
       <c r="B21" t="n">
-        <v>0.111767648150868</v>
+        <v>0.112757380174487</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0404320492867134</v>
+        <v>0.0401081024988206</v>
       </c>
       <c r="D21" t="n">
-        <v>2.76433300123614</v>
+        <v>2.81133669132821</v>
       </c>
       <c r="E21" t="n">
-        <v>0.00571063482188066</v>
+        <v>0.00493975174939752</v>
       </c>
     </row>
     <row r="22">
@@ -806,16 +806,16 @@
         <v>25</v>
       </c>
       <c r="B22" t="n">
-        <v>0.00255785751791987</v>
+        <v>0.0114819011978068</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0212496611956451</v>
+        <v>0.0211953754700939</v>
       </c>
       <c r="D22" t="n">
-        <v>0.120371684723335</v>
+        <v>0.541717282338659</v>
       </c>
       <c r="E22" t="n">
-        <v>0.904190273255382</v>
+        <v>0.588021000568955</v>
       </c>
     </row>
     <row r="23">
@@ -823,16 +823,16 @@
         <v>26</v>
       </c>
       <c r="B23" t="n">
-        <v>0.0013323148534976</v>
+        <v>0.00135172019597867</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0000739115633735702</v>
+        <v>0.0000735004612703312</v>
       </c>
       <c r="D23" t="n">
-        <v>18.0257972188153</v>
+        <v>18.390635549988</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000657045999190251</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000957485261981613</v>
       </c>
     </row>
     <row r="24">
@@ -840,16 +840,16 @@
         <v>27</v>
       </c>
       <c r="B24" t="n">
-        <v>0.00493464879645564</v>
+        <v>0.0034508819704115</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00263782750635342</v>
+        <v>0.00260576250402236</v>
       </c>
       <c r="D24" t="n">
-        <v>1.8707245961194</v>
+        <v>1.3243271269291</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0614020012985199</v>
+        <v>0.18541378089118</v>
       </c>
     </row>
     <row r="25">
@@ -857,16 +857,16 @@
         <v>28</v>
       </c>
       <c r="B25" t="n">
-        <v>0.216481964260779</v>
+        <v>0.207200755583978</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0117245021582973</v>
+        <v>0.011405617192803</v>
       </c>
       <c r="D25" t="n">
-        <v>18.4640645153173</v>
+        <v>18.1665535570247</v>
       </c>
       <c r="E25" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000255525020644238</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000534476360576631</v>
       </c>
     </row>
     <row r="26">
@@ -874,16 +874,16 @@
         <v>29</v>
       </c>
       <c r="B26" t="n">
-        <v>0.00111790889647204</v>
+        <v>-0.00046764123915247</v>
       </c>
       <c r="C26" t="n">
-        <v>0.00244586307383078</v>
+        <v>0.00242990405975558</v>
       </c>
       <c r="D26" t="n">
-        <v>0.457061112060186</v>
+        <v>-0.192452552714987</v>
       </c>
       <c r="E26" t="n">
-        <v>0.647633495262061</v>
+        <v>0.847390229753432</v>
       </c>
     </row>
   </sheetData>
